--- a/backend/arq/search_playlists_top_brasil.xlsx
+++ b/backend/arq/search_playlists_top_brasil.xlsx
@@ -82,7 +82,7 @@
     <t>Novidade todas as semanas, as melhores músicas do momento. Sertanejo, funk, eletrônica, forro, pop. Ana Castela, Gustavo Lima, Wesley Safadão, Marília Mendonça, Jorge e Matheus, Agroplay, Luan Santana, Barretão,Felipe e Rodrigo, Gosta de R Henrique e Juliano, Vulgo Pk,Luana Prado Minha Herança</t>
   </si>
   <si>
-    <t>O MELHOR DO SERTANEJO ESTÁ AQUI #jorgeemateus #mariliamendonça #fernandoesorocaba #wesleysafadao #hugoeguilherme #anacastela #zenetoecristiano #guilhermeebenuto #lauanna #gusttavolima #maiaraemaraisa #diegoevictorhugo #israelerodolfo #henriqueejuliano #matheusekauan #luansantana #murilohuff #2026</t>
+    <t>Clássicos do Sertanejo nas vozes das maiores duplas do Brasil 🤠 #zezedicamargo #leandroeleonardo #chitaozinhoexororo #sertanejo #modao #raiz #brasil #musicapopular</t>
   </si>
   <si>
     <t>SERTANEJO 2026 🍺 ATUALIZADO ABRIL 2026 | SERTANEJO MAIS TOCADAS | TOP SERTANEJO 2026</t>
@@ -121,19 +121,19 @@
     <t>6dPXEpme2V9vL8WUmEZe5G</t>
   </si>
   <si>
-    <t>[{'height': None, 'url': 'https://image-cdn-ak.spotifycdn.com/image/ab67706c0000da840ab6bf9f6b99c8067ce53a30', 'width': None}]</t>
+    <t>[{'height': None, 'url': 'https://image-cdn-ak.spotifycdn.com/image/ab67706c0000d72c0ab6bf9f6b99c8067ce53a30', 'width': None}]</t>
   </si>
   <si>
     <t>[{'height': None, 'url': 'https://image-cdn-ak.spotifycdn.com/image/ab67706c0000da84a7a1cb0a0d9432aa0b3d6489', 'width': None}]</t>
   </si>
   <si>
-    <t>[{'height': None, 'url': 'https://image-cdn-ak.spotifycdn.com/image/ab67706c0000da8407a338b694f6a2addd1aca95', 'width': None}]</t>
+    <t>[{'height': None, 'url': 'https://image-cdn-ak.spotifycdn.com/image/ab67706c0000d72c5d99a6c862756023218723f0', 'width': None}]</t>
   </si>
   <si>
     <t>[{'height': None, 'url': 'https://image-cdn-ak.spotifycdn.com/image/ab67706c0000da846895b443afa2d42520a38eaa', 'width': None}]</t>
   </si>
   <si>
-    <t>[{'height': None, 'url': 'https://image-cdn-fa.spotifycdn.com/image/ab67706c0000d72c6423f83ff232f29592865a5c', 'width': None}]</t>
+    <t>[{'height': None, 'url': 'https://image-cdn-ak.spotifycdn.com/image/ab67706c0000d72c6423f83ff232f29592865a5c', 'width': None}]</t>
   </si>
   <si>
     <t>BRASIL 2026 - AS MELHORES E MAIS TOCADAS</t>
@@ -142,25 +142,25 @@
     <t>Top Brasil🔥As Mais Tocadas 2026🔥 Só Toca Top🔥 Só As Melhores🔥Verão🔥</t>
   </si>
   <si>
-    <t>TOP SERTANEJO  | Mais Tocadas | 2026 |  As Tops do Brasil</t>
+    <t>Clássicos Sertanejo | Amigos</t>
   </si>
   <si>
     <t>SERTANEJO 2026  ⭐ TOP 100 MAIS TOCADAS</t>
   </si>
   <si>
-    <t>AAApr/F9wroUvV/TN+ANNFM2YruvDTJM</t>
+    <t>AAApuJ5xBKgEgvluhGcXPFoOXYFw0UmE</t>
   </si>
   <si>
     <t>AAAWRnnUxcYR4aBB3xjP28lJjaBbupyH</t>
   </si>
   <si>
-    <t>AAAYJfKRhWr0PW3v7X+60UkicEqAJm4b</t>
-  </si>
-  <si>
-    <t>AAAZwPHw4SD4+RV2jD0MuP769HtBN6j5</t>
-  </si>
-  <si>
-    <t>AAAEjWl+/8BWyD6iSgYqES5P3ukalqt+</t>
+    <t>AAAYiU6QsoEX4O6WA3b6ALVsjqDGASr4</t>
+  </si>
+  <si>
+    <t>AAAZ05IKGdh3h61XxyCvKqy54CAdCJBc</t>
+  </si>
+  <si>
+    <t>AAAFDKJGyUbA1MTIIdBHPHK3i8ZFZWUS</t>
   </si>
   <si>
     <t>playlist</t>
@@ -893,7 +893,7 @@
         <v>87</v>
       </c>
       <c r="T6">
-        <v>96</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -952,7 +952,7 @@
         <v>88</v>
       </c>
       <c r="T7">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1011,7 +1011,7 @@
         <v>89</v>
       </c>
       <c r="T10">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/backend/arq/search_playlists_top_brasil.xlsx
+++ b/backend/arq/search_playlists_top_brasil.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="91">
   <si>
     <t>collaborative</t>
   </si>
@@ -82,13 +82,13 @@
     <t>Novidade todas as semanas, as melhores músicas do momento. Sertanejo, funk, eletrônica, forro, pop. Ana Castela, Gustavo Lima, Wesley Safadão, Marília Mendonça, Jorge e Matheus, Agroplay, Luan Santana, Barretão,Felipe e Rodrigo, Gosta de R Henrique e Juliano, Vulgo Pk,Luana Prado Minha Herança</t>
   </si>
   <si>
+    <t>✅ Atualizada | Mais tocadas | Melhores lançamentos Top Brasil de 2026 | lG: @matheusfcalixto | Imagem: Gusttavo Lima, Ana Castela, Henrique e Juliano.</t>
+  </si>
+  <si>
     <t>Clássicos do Sertanejo nas vozes das maiores duplas do Brasil 🤠 #zezedicamargo #leandroeleonardo #chitaozinhoexororo #sertanejo #modao #raiz #brasil #musicapopular</t>
   </si>
   <si>
-    <t>SERTANEJO 2026 🍺 ATUALIZADO ABRIL 2026 | SERTANEJO MAIS TOCADAS | TOP SERTANEJO 2026</t>
-  </si>
-  <si>
-    <t>Ouça aqui as melhores músicas sertanejas do momento! Clique no ➕ para seguir a playlist! Sertanejo 2025&amp;#x2F;2026 Atualizado - Gustavo Lima - Murilo Huff - Maiara e Maraisa - Matheus e Kauan - Simone Mendes - Hugo e Guilherme - Jorge e Mateus - Henrique  e Juliano - Luan Pereira - Ana Castela!</t>
+    <t xml:space="preserve">Ouça aqui as melhores músicas de diversos gêneros no Brasil em 2026! Mais tocadas Brasil - playlist Brasil - música Brasil 2026 - Lançamentos 2026 - Hits do momento - Top 100 Brasil - Sucessos nacionais - Músicas populares - Novidades musicais - Melhores do ano - Paradas de sucesso </t>
   </si>
   <si>
     <t>https://api.spotify.com/v1/playlists/1msY3c9fzgE3V11aNhsq2O</t>
@@ -97,13 +97,13 @@
     <t>https://api.spotify.com/v1/playlists/2YnARIUCi8jOPDncFFwMtf</t>
   </si>
   <si>
+    <t>https://api.spotify.com/v1/playlists/1tOrLjlSB49vMA9jasoat8</t>
+  </si>
+  <si>
     <t>https://api.spotify.com/v1/playlists/6sAINczI3JLesEgQ2hLa19</t>
   </si>
   <si>
-    <t>https://api.spotify.com/v1/playlists/7110oQdXKCBofaBanEYo1Z</t>
-  </si>
-  <si>
-    <t>https://api.spotify.com/v1/playlists/6dPXEpme2V9vL8WUmEZe5G</t>
+    <t>https://api.spotify.com/v1/playlists/63U9g8H5bxDa7X2sQs8wdq</t>
   </si>
   <si>
     <t>1msY3c9fzgE3V11aNhsq2O</t>
@@ -112,28 +112,28 @@
     <t>2YnARIUCi8jOPDncFFwMtf</t>
   </si>
   <si>
+    <t>1tOrLjlSB49vMA9jasoat8</t>
+  </si>
+  <si>
     <t>6sAINczI3JLesEgQ2hLa19</t>
   </si>
   <si>
-    <t>7110oQdXKCBofaBanEYo1Z</t>
-  </si>
-  <si>
-    <t>6dPXEpme2V9vL8WUmEZe5G</t>
-  </si>
-  <si>
-    <t>[{'height': None, 'url': 'https://image-cdn-ak.spotifycdn.com/image/ab67706c0000d72c0ab6bf9f6b99c8067ce53a30', 'width': None}]</t>
+    <t>63U9g8H5bxDa7X2sQs8wdq</t>
+  </si>
+  <si>
+    <t>[{'height': None, 'url': 'https://image-cdn-ak.spotifycdn.com/image/ab67706c0000da840ab6bf9f6b99c8067ce53a30', 'width': None}]</t>
   </si>
   <si>
     <t>[{'height': None, 'url': 'https://image-cdn-ak.spotifycdn.com/image/ab67706c0000da84a7a1cb0a0d9432aa0b3d6489', 'width': None}]</t>
   </si>
   <si>
-    <t>[{'height': None, 'url': 'https://image-cdn-ak.spotifycdn.com/image/ab67706c0000d72c5d99a6c862756023218723f0', 'width': None}]</t>
-  </si>
-  <si>
-    <t>[{'height': None, 'url': 'https://image-cdn-ak.spotifycdn.com/image/ab67706c0000da846895b443afa2d42520a38eaa', 'width': None}]</t>
-  </si>
-  <si>
-    <t>[{'height': None, 'url': 'https://image-cdn-ak.spotifycdn.com/image/ab67706c0000d72c6423f83ff232f29592865a5c', 'width': None}]</t>
+    <t>[{'height': None, 'url': 'https://image-cdn-ak.spotifycdn.com/image/ab67706c0000da846e0ef5e5d55605b109d05547', 'width': None}]</t>
+  </si>
+  <si>
+    <t>[{'height': None, 'url': 'https://image-cdn-ak.spotifycdn.com/image/ab67706c0000da845d99a6c862756023218723f0', 'width': None}]</t>
+  </si>
+  <si>
+    <t>[{'height': None, 'url': 'https://image-cdn-ak.spotifycdn.com/image/ab67706c0000da84a6acfa943568b90a13e30011', 'width': None}]</t>
   </si>
   <si>
     <t>BRASIL 2026 - AS MELHORES E MAIS TOCADAS</t>
@@ -142,10 +142,13 @@
     <t>Top Brasil🔥As Mais Tocadas 2026🔥 Só Toca Top🔥 Só As Melhores🔥Verão🔥</t>
   </si>
   <si>
+    <t>TOP BRASIL 🚀ABRIL 2026 | MAIS TOCADAS | LANÇAMENTOS💥</t>
+  </si>
+  <si>
     <t>Clássicos Sertanejo | Amigos</t>
   </si>
   <si>
-    <t>SERTANEJO 2026  ⭐ TOP 100 MAIS TOCADAS</t>
+    <t>MAIS TOCADAS 2026 ⭐  MELHORES HITS BRASIL</t>
   </si>
   <si>
     <t>AAApuJ5xBKgEgvluhGcXPFoOXYFw0UmE</t>
@@ -154,13 +157,13 @@
     <t>AAAWRnnUxcYR4aBB3xjP28lJjaBbupyH</t>
   </si>
   <si>
+    <t>AAAWKtiCE5wQqz61Y+36mDbIukQd8y5p</t>
+  </si>
+  <si>
     <t>AAAYiU6QsoEX4O6WA3b6ALVsjqDGASr4</t>
   </si>
   <si>
-    <t>AAAZ05IKGdh3h61XxyCvKqy54CAdCJBc</t>
-  </si>
-  <si>
-    <t>AAAFDKJGyUbA1MTIIdBHPHK3i8ZFZWUS</t>
+    <t>AAAFxnDqlDblfw3FoB4y89MGYOQxifeg</t>
   </si>
   <si>
     <t>playlist</t>
@@ -172,13 +175,13 @@
     <t>spotify:playlist:2YnARIUCi8jOPDncFFwMtf</t>
   </si>
   <si>
+    <t>spotify:playlist:1tOrLjlSB49vMA9jasoat8</t>
+  </si>
+  <si>
     <t>spotify:playlist:6sAINczI3JLesEgQ2hLa19</t>
   </si>
   <si>
-    <t>spotify:playlist:7110oQdXKCBofaBanEYo1Z</t>
-  </si>
-  <si>
-    <t>spotify:playlist:6dPXEpme2V9vL8WUmEZe5G</t>
+    <t>spotify:playlist:63U9g8H5bxDa7X2sQs8wdq</t>
   </si>
   <si>
     <t>https://open.spotify.com/playlist/1msY3c9fzgE3V11aNhsq2O</t>
@@ -187,13 +190,13 @@
     <t>https://open.spotify.com/playlist/2YnARIUCi8jOPDncFFwMtf</t>
   </si>
   <si>
+    <t>https://open.spotify.com/playlist/1tOrLjlSB49vMA9jasoat8</t>
+  </si>
+  <si>
     <t>https://open.spotify.com/playlist/6sAINczI3JLesEgQ2hLa19</t>
   </si>
   <si>
-    <t>https://open.spotify.com/playlist/7110oQdXKCBofaBanEYo1Z</t>
-  </si>
-  <si>
-    <t>https://open.spotify.com/playlist/6dPXEpme2V9vL8WUmEZe5G</t>
+    <t>https://open.spotify.com/playlist/63U9g8H5bxDa7X2sQs8wdq</t>
   </si>
   <si>
     <t>22tpv6ginr2rtnelnchjmy3eq</t>
@@ -202,13 +205,13 @@
     <t>Amber</t>
   </si>
   <si>
+    <t>Matheus Calixto</t>
+  </si>
+  <si>
     <t>DOCTOR HITS | Playlists ®</t>
   </si>
   <si>
-    <t>DaKoTa</t>
-  </si>
-  <si>
-    <t>Kleber Santiago</t>
+    <t>Andre</t>
   </si>
   <si>
     <t>https://open.spotify.com/user/22tpv6ginr2rtnelnchjmy3eq</t>
@@ -217,13 +220,13 @@
     <t>https://open.spotify.com/user/22hprksnarb4ljlky4ypi5qry</t>
   </si>
   <si>
+    <t>https://open.spotify.com/user/22j64ff2lcr325lrcmn5qzfoi</t>
+  </si>
+  <si>
     <t>https://open.spotify.com/user/davis_olympio</t>
   </si>
   <si>
-    <t>https://open.spotify.com/user/22bmg3caiyohqjlgru6kevrha</t>
-  </si>
-  <si>
-    <t>https://open.spotify.com/user/31xdrdu6dsul2wax2hmnesysjeui</t>
+    <t>https://open.spotify.com/user/315hkzf4ange2gznwo6uc4fuc36y</t>
   </si>
   <si>
     <t>https://api.spotify.com/v1/users/22tpv6ginr2rtnelnchjmy3eq</t>
@@ -232,25 +235,25 @@
     <t>https://api.spotify.com/v1/users/22hprksnarb4ljlky4ypi5qry</t>
   </si>
   <si>
+    <t>https://api.spotify.com/v1/users/22j64ff2lcr325lrcmn5qzfoi</t>
+  </si>
+  <si>
     <t>https://api.spotify.com/v1/users/davis_olympio</t>
   </si>
   <si>
-    <t>https://api.spotify.com/v1/users/22bmg3caiyohqjlgru6kevrha</t>
-  </si>
-  <si>
-    <t>https://api.spotify.com/v1/users/31xdrdu6dsul2wax2hmnesysjeui</t>
+    <t>https://api.spotify.com/v1/users/315hkzf4ange2gznwo6uc4fuc36y</t>
   </si>
   <si>
     <t>22hprksnarb4ljlky4ypi5qry</t>
   </si>
   <si>
+    <t>22j64ff2lcr325lrcmn5qzfoi</t>
+  </si>
+  <si>
     <t>davis_olympio</t>
   </si>
   <si>
-    <t>22bmg3caiyohqjlgru6kevrha</t>
-  </si>
-  <si>
-    <t>31xdrdu6dsul2wax2hmnesysjeui</t>
+    <t>315hkzf4ange2gznwo6uc4fuc36y</t>
   </si>
   <si>
     <t>user</t>
@@ -262,13 +265,13 @@
     <t>spotify:user:22hprksnarb4ljlky4ypi5qry</t>
   </si>
   <si>
+    <t>spotify:user:22j64ff2lcr325lrcmn5qzfoi</t>
+  </si>
+  <si>
     <t>spotify:user:davis_olympio</t>
   </si>
   <si>
-    <t>spotify:user:22bmg3caiyohqjlgru6kevrha</t>
-  </si>
-  <si>
-    <t>spotify:user:31xdrdu6dsul2wax2hmnesysjeui</t>
+    <t>spotify:user:315hkzf4ange2gznwo6uc4fuc36y</t>
   </si>
   <si>
     <t>https://api.spotify.com/v1/playlists/1msY3c9fzgE3V11aNhsq2O/items</t>
@@ -277,13 +280,13 @@
     <t>https://api.spotify.com/v1/playlists/2YnARIUCi8jOPDncFFwMtf/items</t>
   </si>
   <si>
+    <t>https://api.spotify.com/v1/playlists/1tOrLjlSB49vMA9jasoat8/items</t>
+  </si>
+  <si>
     <t>https://api.spotify.com/v1/playlists/6sAINczI3JLesEgQ2hLa19/items</t>
   </si>
   <si>
-    <t>https://api.spotify.com/v1/playlists/7110oQdXKCBofaBanEYo1Z/items</t>
-  </si>
-  <si>
-    <t>https://api.spotify.com/v1/playlists/6dPXEpme2V9vL8WUmEZe5G/items</t>
+    <t>https://api.spotify.com/v1/playlists/63U9g8H5bxDa7X2sQs8wdq/items</t>
   </si>
 </sst>
 </file>
@@ -654,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -742,37 +745,37 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T4">
         <v>150</v>
@@ -801,37 +804,37 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T5">
         <v>81</v>
@@ -860,40 +863,40 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T6">
-        <v>67</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -913,105 +916,105 @@
         <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M7" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P7" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>80</v>
+      </c>
+      <c r="R7" t="s">
+        <v>84</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="T7">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" t="b">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
         <v>49</v>
       </c>
-      <c r="K7" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="M7" t="s">
-        <v>63</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P7" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q7" t="s">
+      <c r="J8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" t="s">
+        <v>65</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="P8" t="s">
         <v>79</v>
       </c>
-      <c r="R7" t="s">
-        <v>83</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="T7">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
-      <c r="A10" t="b">
-        <v>0</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" t="s">
-        <v>49</v>
-      </c>
-      <c r="K10" t="s">
-        <v>54</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="M10" t="s">
-        <v>64</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="P10" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>79</v>
-      </c>
-      <c r="R10" t="s">
-        <v>84</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="T10">
-        <v>124</v>
+      <c r="Q8" t="s">
+        <v>80</v>
+      </c>
+      <c r="R8" t="s">
+        <v>85</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="T8">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1036,11 +1039,11 @@
     <hyperlink ref="N7" r:id="rId18"/>
     <hyperlink ref="O7" r:id="rId19"/>
     <hyperlink ref="S7" r:id="rId20"/>
-    <hyperlink ref="C10" r:id="rId21"/>
-    <hyperlink ref="L10" r:id="rId22"/>
-    <hyperlink ref="N10" r:id="rId23"/>
-    <hyperlink ref="O10" r:id="rId24"/>
-    <hyperlink ref="S10" r:id="rId25"/>
+    <hyperlink ref="C8" r:id="rId21"/>
+    <hyperlink ref="L8" r:id="rId22"/>
+    <hyperlink ref="N8" r:id="rId23"/>
+    <hyperlink ref="O8" r:id="rId24"/>
+    <hyperlink ref="S8" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
